--- a/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-14557_Vocabulary_Validation.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-14557_Vocabulary_Validation.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="77">
   <si>
     <t>Datatype Gender &lt;String&gt;</t>
   </si>
@@ -249,6 +249,21 @@
   </si>
   <si>
     <t>= SomeMethod1(10, "Test199", "test19")</t>
+  </si>
+  <si>
+    <t>Spreadsheet SpreadsheetResult check(Country[] country)</t>
+  </si>
+  <si>
+    <t>Datatype Country &lt;String&gt;</t>
+  </si>
+  <si>
+    <t>NJ</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>= check(new String[]{"NJ", "AB"})</t>
   </si>
 </sst>
 </file>
@@ -898,7 +913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B4:E60"/>
+  <dimension ref="B4:E65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="2.83203125"/>
@@ -915,21 +930,9 @@
     <col min="12" max="16384" style="1" width="9.1640625"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:2">
-      <c r="B4" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2">
-      <c r="B5" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2">
-      <c r="B6" s="12" t="s">
-        <v>42</v>
-      </c>
-    </row>
+    <row r="4" spans="2:2"/>
+    <row r="5" spans="2:2"/>
+    <row r="6" spans="2:2"/>
     <row r="8" spans="2:2">
       <c r="B8" s="12" t="s">
         <v>13</v>
@@ -1048,7 +1051,7 @@
     <row r="25" spans="2:5" ht="14" thickTop="1"/>
     <row r="27" spans="2:5">
       <c r="B27" s="16" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -1207,7 +1210,7 @@
         <v>48</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>60</v>
@@ -1310,6 +1313,26 @@
       </c>
     </row>
     <row r="60" spans="2:4" ht="14" thickTop="1"/>
+    <row r="62">
+      <c r="B62" t="s" s="12">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="s" s="12">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B22:D22"/>
